--- a/Football_Player_Match_and_Totals.xlsx
+++ b/Football_Player_Match_and_Totals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/78878cf66f9e0fad/Football/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2582" documentId="13_ncr:1_{D0682A70-CFBA-4557-AA8E-351EA0D15F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8249730-3557-4D13-A70C-157793FF23CD}"/>
+  <xr:revisionPtr revIDLastSave="2643" documentId="13_ncr:1_{D0682A70-CFBA-4557-AA8E-351EA0D15F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{137626C7-722D-43D0-8BA1-500A3B0FACFC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="13" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="102">
   <si>
     <t>Date</t>
   </si>
@@ -369,6 +369,9 @@
   <si>
     <t>9 X 6</t>
   </si>
+  <si>
+    <t>3 X 2</t>
+  </si>
 </sst>
 </file>
 
@@ -513,7 +516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -549,6 +552,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1134,174 +1140,6 @@
       <alignment vertical="center"/>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -1483,6 +1321,174 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1496,14 +1502,18 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Marcus Vardi" refreshedDate="46182.827357291666" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="270" xr:uid="{2C3B15CE-11B4-460F-ADFB-7994C94CC10E}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Marcus Vardi" refreshedDate="46189.738056828704" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="284" xr:uid="{2C3B15CE-11B4-460F-ADFB-7994C94CC10E}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table1"/>
   </cacheSource>
   <cacheFields count="10">
     <cacheField name="Date" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-19T00:00:00" maxDate="2026-06-09T00:00:00" count="19">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-19T00:00:00" maxDate="2026-06-16T00:00:00" count="20">
         <d v="2026-01-19T00:00:00"/>
         <d v="2026-01-26T00:00:00"/>
         <d v="2026-02-02T00:00:00"/>
@@ -1523,6 +1533,7 @@
         <d v="2026-05-18T00:00:00"/>
         <d v="2026-06-01T00:00:00"/>
         <d v="2026-06-08T00:00:00"/>
+        <d v="2026-06-15T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Score" numFmtId="0">
@@ -1614,7 +1625,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="270">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="284">
   <r>
     <x v="0"/>
     <s v="4 x 2 "/>
@@ -4847,6 +4858,174 @@
     <x v="18"/>
     <s v="9 X 6"/>
     <x v="22"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="7"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="18"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="15"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3000"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="24"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="32"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="13"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1001"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="14"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1000"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="8"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="12"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="3 X 2"/>
+    <x v="10"/>
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
@@ -4863,7 +5042,7 @@
   <location ref="A3:I37" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField axis="axisPage" numFmtId="14" showAll="0">
-      <items count="20">
+      <items count="21">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -4883,6 +5062,7 @@
         <item x="16"/>
         <item x="17"/>
         <item x="18"/>
+        <item x="19"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4965,22 +5145,19 @@
   </rowFields>
   <rowItems count="34">
     <i>
-      <x v="25"/>
+      <x v="40"/>
     </i>
     <i>
-      <x v="40"/>
+      <x v="25"/>
     </i>
     <i>
       <x v="12"/>
     </i>
     <i>
-      <x v="36"/>
-    </i>
-    <i>
       <x v="41"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="36"/>
     </i>
     <i>
       <x v="39"/>
@@ -4990,6 +5167,9 @@
     </i>
     <i>
       <x v="24"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i>
       <x v="46"/>
@@ -5010,6 +5190,9 @@
       <x v="47"/>
     </i>
     <i>
+      <x v="42"/>
+    </i>
+    <i>
       <x v="48"/>
     </i>
     <i>
@@ -5022,31 +5205,28 @@
       <x v="21"/>
     </i>
     <i>
-      <x v="42"/>
-    </i>
-    <i>
       <x/>
     </i>
     <i>
       <x v="28"/>
     </i>
     <i>
-      <x v="37"/>
+      <x v="44"/>
     </i>
     <i>
       <x v="27"/>
     </i>
     <i>
-      <x v="44"/>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="50"/>
     </i>
     <i>
       <x v="16"/>
     </i>
     <i>
       <x v="20"/>
-    </i>
-    <i>
-      <x v="50"/>
     </i>
     <i>
       <x v="34"/>
@@ -5110,105 +5290,6 @@
     <dataField name="Sum of Ordem" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="30">
-    <format dxfId="95">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="94">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="93">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="92">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="91">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="90">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="6">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="5"/>
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="89">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="88">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="87">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="86">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="85">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="84">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="6">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="5"/>
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="83">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="82">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="81">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="80">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="79">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="78">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="6">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="5"/>
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
     <format dxfId="77">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
@@ -5262,6 +5343,105 @@
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="66">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="6">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="5"/>
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="65">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="64">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="63">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="62">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="61">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="60">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="6">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="5"/>
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="59">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="58">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="57">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="56">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="55">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="54">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="6">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="5"/>
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="53">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="51">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="49">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="6">
@@ -5434,13 +5614,13 @@
       <x v="12"/>
     </i>
     <i>
+      <x v="41"/>
+    </i>
+    <i>
       <x v="3"/>
     </i>
     <i>
       <x v="25"/>
-    </i>
-    <i>
-      <x v="41"/>
     </i>
     <i>
       <x v="46"/>
@@ -5449,10 +5629,10 @@
       <x v="48"/>
     </i>
     <i>
-      <x v="24"/>
+      <x v="36"/>
     </i>
     <i>
-      <x v="36"/>
+      <x v="24"/>
     </i>
     <i>
       <x v="6"/>
@@ -5467,6 +5647,9 @@
       <x v="40"/>
     </i>
     <i>
+      <x v="42"/>
+    </i>
+    <i>
       <x v="28"/>
     </i>
     <i>
@@ -5474,9 +5657,6 @@
     </i>
     <i>
       <x v="39"/>
-    </i>
-    <i>
-      <x v="42"/>
     </i>
     <i>
       <x v="2"/>
@@ -5550,70 +5730,70 @@
     <dataField name="Sum of Ordem" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="18">
-    <format dxfId="65">
+    <format dxfId="107">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="64">
+    <format dxfId="106">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="63">
+    <format dxfId="105">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="62">
+    <format dxfId="104">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="103">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="102">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="101">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="100">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="57">
+    <format dxfId="99">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="98">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="97">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="96">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="95">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="94">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="93">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="92">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="49">
+    <format dxfId="91">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="90">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -5659,19 +5839,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{735DA0A5-6880-483E-9C8F-43C40DE943EF}" name="Table1" displayName="Table1" ref="A1:J271" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106">
-  <autoFilter ref="A1:J271" xr:uid="{735DA0A5-6880-483E-9C8F-43C40DE943EF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{735DA0A5-6880-483E-9C8F-43C40DE943EF}" name="Table1" displayName="Table1" ref="A1:J285" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
+  <autoFilter ref="A1:J285" xr:uid="{735DA0A5-6880-483E-9C8F-43C40DE943EF}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{7E0F6817-3C5F-45D3-85D1-7223CC22CE68}" name="Date" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{6D8ED8CE-D07F-4EEA-B56E-B67FEBCBFCFD}" name="Score" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{16052D71-92F1-4811-AE00-9A1106245504}" name="Player" dataDxfId="103"/>
-    <tableColumn id="4" xr3:uid="{810D6873-D6B2-40F5-8880-A98EC577F5A6}" name="Goals" dataDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{A8AF9823-CBF7-48EF-A740-3D090DA2ABBD}" name="Assists" dataDxfId="101"/>
-    <tableColumn id="6" xr3:uid="{F26A9730-0FD1-4540-8371-94440A47D869}" name="Vitoria " dataDxfId="100"/>
-    <tableColumn id="7" xr3:uid="{22D029AE-DC8A-4A10-8C8D-BAFD27E75BC9}" name="Derrota" dataDxfId="99"/>
-    <tableColumn id="8" xr3:uid="{F7519543-D12A-4A5D-9752-EC65B294C616}" name="Empate" dataDxfId="98"/>
-    <tableColumn id="10" xr3:uid="{1D9271D0-3ED1-4736-8F48-89B694EC47A7}" name="Time misto" dataDxfId="97"/>
-    <tableColumn id="9" xr3:uid="{65967A72-F917-4A11-8E74-B48CED95D07B}" name="Ordem" dataDxfId="96">
+    <tableColumn id="1" xr3:uid="{7E0F6817-3C5F-45D3-85D1-7223CC22CE68}" name="Date" dataDxfId="87"/>
+    <tableColumn id="2" xr3:uid="{6D8ED8CE-D07F-4EEA-B56E-B67FEBCBFCFD}" name="Score" dataDxfId="86"/>
+    <tableColumn id="3" xr3:uid="{16052D71-92F1-4811-AE00-9A1106245504}" name="Player" dataDxfId="85"/>
+    <tableColumn id="4" xr3:uid="{810D6873-D6B2-40F5-8880-A98EC577F5A6}" name="Goals" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{A8AF9823-CBF7-48EF-A740-3D090DA2ABBD}" name="Assists" dataDxfId="83"/>
+    <tableColumn id="6" xr3:uid="{F26A9730-0FD1-4540-8371-94440A47D869}" name="Vitoria " dataDxfId="82"/>
+    <tableColumn id="7" xr3:uid="{22D029AE-DC8A-4A10-8C8D-BAFD27E75BC9}" name="Derrota" dataDxfId="81"/>
+    <tableColumn id="8" xr3:uid="{F7519543-D12A-4A5D-9752-EC65B294C616}" name="Empate" dataDxfId="80"/>
+    <tableColumn id="10" xr3:uid="{1D9271D0-3ED1-4736-8F48-89B694EC47A7}" name="Time misto" dataDxfId="79"/>
+    <tableColumn id="9" xr3:uid="{65967A72-F917-4A11-8E74-B48CED95D07B}" name="Ordem" dataDxfId="78">
       <calculatedColumnFormula>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6172,7 +6352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J271"/>
+  <dimension ref="A1:J285"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="4" customWidth="1"/>
@@ -15120,6 +15300,468 @@
         <v>0</v>
       </c>
       <c r="J271" s="4">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A272" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D272" s="4">
+        <v>0</v>
+      </c>
+      <c r="E272" s="4">
+        <v>0</v>
+      </c>
+      <c r="F272" s="4">
+        <v>1</v>
+      </c>
+      <c r="G272" s="4">
+        <v>0</v>
+      </c>
+      <c r="H272" s="4">
+        <v>0</v>
+      </c>
+      <c r="I272" s="4">
+        <v>0</v>
+      </c>
+      <c r="J272" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A273" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D273" s="4">
+        <v>0</v>
+      </c>
+      <c r="E273" s="4">
+        <v>1</v>
+      </c>
+      <c r="F273" s="4">
+        <v>1</v>
+      </c>
+      <c r="G273" s="4">
+        <v>0</v>
+      </c>
+      <c r="H273" s="4">
+        <v>0</v>
+      </c>
+      <c r="I273" s="4">
+        <v>0</v>
+      </c>
+      <c r="J273" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A274" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D274" s="4">
+        <v>0</v>
+      </c>
+      <c r="E274" s="4">
+        <v>1</v>
+      </c>
+      <c r="F274" s="4">
+        <v>1</v>
+      </c>
+      <c r="G274" s="4">
+        <v>0</v>
+      </c>
+      <c r="H274" s="4">
+        <v>0</v>
+      </c>
+      <c r="I274" s="4">
+        <v>0</v>
+      </c>
+      <c r="J274" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A275" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D275" s="4">
+        <v>0</v>
+      </c>
+      <c r="E275" s="4">
+        <v>1</v>
+      </c>
+      <c r="F275" s="4">
+        <v>1</v>
+      </c>
+      <c r="G275" s="4">
+        <v>0</v>
+      </c>
+      <c r="H275" s="4">
+        <v>0</v>
+      </c>
+      <c r="I275" s="4">
+        <v>0</v>
+      </c>
+      <c r="J275" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A276" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D276" s="4">
+        <v>3</v>
+      </c>
+      <c r="E276" s="4">
+        <v>0</v>
+      </c>
+      <c r="F276" s="4">
+        <v>1</v>
+      </c>
+      <c r="G276" s="4">
+        <v>0</v>
+      </c>
+      <c r="H276" s="4">
+        <v>0</v>
+      </c>
+      <c r="I276" s="4">
+        <v>0</v>
+      </c>
+      <c r="J276" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A277" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D277" s="4">
+        <v>0</v>
+      </c>
+      <c r="E277" s="4">
+        <v>0</v>
+      </c>
+      <c r="F277" s="4">
+        <v>1</v>
+      </c>
+      <c r="G277" s="4">
+        <v>0</v>
+      </c>
+      <c r="H277" s="4">
+        <v>0</v>
+      </c>
+      <c r="I277" s="4">
+        <v>0</v>
+      </c>
+      <c r="J277" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A278" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D278" s="4">
+        <v>0</v>
+      </c>
+      <c r="E278" s="4">
+        <v>0</v>
+      </c>
+      <c r="F278" s="4">
+        <v>1</v>
+      </c>
+      <c r="G278" s="4">
+        <v>0</v>
+      </c>
+      <c r="H278" s="4">
+        <v>0</v>
+      </c>
+      <c r="I278" s="4">
+        <v>0</v>
+      </c>
+      <c r="J278" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A279" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D279" s="4">
+        <v>0</v>
+      </c>
+      <c r="E279" s="4">
+        <v>0</v>
+      </c>
+      <c r="F279" s="4">
+        <v>0</v>
+      </c>
+      <c r="G279" s="4">
+        <v>1</v>
+      </c>
+      <c r="H279" s="4">
+        <v>0</v>
+      </c>
+      <c r="I279" s="4">
+        <v>0</v>
+      </c>
+      <c r="J279" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A280" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D280" s="4">
+        <v>1</v>
+      </c>
+      <c r="E280" s="4">
+        <v>1</v>
+      </c>
+      <c r="F280" s="4">
+        <v>0</v>
+      </c>
+      <c r="G280" s="4">
+        <v>1</v>
+      </c>
+      <c r="H280" s="4">
+        <v>0</v>
+      </c>
+      <c r="I280" s="4">
+        <v>0</v>
+      </c>
+      <c r="J280" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A281" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D281" s="4">
+        <v>0</v>
+      </c>
+      <c r="E281" s="4">
+        <v>0</v>
+      </c>
+      <c r="F281" s="4">
+        <v>0</v>
+      </c>
+      <c r="G281" s="4">
+        <v>1</v>
+      </c>
+      <c r="H281" s="4">
+        <v>0</v>
+      </c>
+      <c r="I281" s="4">
+        <v>0</v>
+      </c>
+      <c r="J281" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A282" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D282" s="4">
+        <v>1</v>
+      </c>
+      <c r="E282" s="4">
+        <v>0</v>
+      </c>
+      <c r="F282" s="4">
+        <v>0</v>
+      </c>
+      <c r="G282" s="4">
+        <v>1</v>
+      </c>
+      <c r="H282" s="4">
+        <v>0</v>
+      </c>
+      <c r="I282" s="4">
+        <v>0</v>
+      </c>
+      <c r="J282" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A283" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D283" s="4">
+        <v>0</v>
+      </c>
+      <c r="E283" s="4">
+        <v>0</v>
+      </c>
+      <c r="F283" s="4">
+        <v>0</v>
+      </c>
+      <c r="G283" s="4">
+        <v>1</v>
+      </c>
+      <c r="H283" s="4">
+        <v>0</v>
+      </c>
+      <c r="I283" s="4">
+        <v>0</v>
+      </c>
+      <c r="J283" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A284" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D284" s="4">
+        <v>0</v>
+      </c>
+      <c r="E284" s="4">
+        <v>1</v>
+      </c>
+      <c r="F284" s="4">
+        <v>0</v>
+      </c>
+      <c r="G284" s="4">
+        <v>1</v>
+      </c>
+      <c r="H284" s="4">
+        <v>0</v>
+      </c>
+      <c r="I284" s="4">
+        <v>0</v>
+      </c>
+      <c r="J284" s="19">
+        <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A285" s="5">
+        <v>46188</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D285" s="4">
+        <v>0</v>
+      </c>
+      <c r="E285" s="4">
+        <v>0</v>
+      </c>
+      <c r="F285" s="4">
+        <v>0</v>
+      </c>
+      <c r="G285" s="4">
+        <v>1</v>
+      </c>
+      <c r="H285" s="4">
+        <v>0</v>
+      </c>
+      <c r="I285" s="4">
+        <v>0</v>
+      </c>
+      <c r="J285" s="19">
         <f>Table1[[#This Row],[Goals]]*1000 + Table1[[#This Row],[Assists]]</f>
         <v>0</v>
       </c>
@@ -15142,12 +15784,12 @@
   <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="1" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="1"/>
@@ -15192,291 +15834,291 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="19">
+        <v>54</v>
+      </c>
+      <c r="B4" s="20">
         <v>18</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="20">
         <v>7</v>
       </c>
-      <c r="D4" s="19">
-        <v>7</v>
-      </c>
-      <c r="E4" s="19">
-        <v>3</v>
-      </c>
-      <c r="F4" s="19">
-        <v>1</v>
-      </c>
-      <c r="G4" s="19">
-        <v>17</v>
-      </c>
-      <c r="H4" s="19">
-        <v>24</v>
-      </c>
-      <c r="I4" s="19">
-        <v>17024</v>
+      <c r="D4" s="20">
+        <v>8</v>
+      </c>
+      <c r="E4" s="20">
+        <v>2</v>
+      </c>
+      <c r="F4" s="20">
+        <v>1</v>
+      </c>
+      <c r="G4" s="20">
+        <v>5</v>
+      </c>
+      <c r="H4" s="20">
+        <v>5</v>
+      </c>
+      <c r="I4" s="20">
+        <v>5005</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="19">
+        <v>40</v>
+      </c>
+      <c r="B5" s="20">
+        <v>18</v>
+      </c>
+      <c r="C5" s="20">
+        <v>7</v>
+      </c>
+      <c r="D5" s="20">
+        <v>7</v>
+      </c>
+      <c r="E5" s="20">
+        <v>3</v>
+      </c>
+      <c r="F5" s="20">
+        <v>1</v>
+      </c>
+      <c r="G5" s="20">
         <v>17</v>
       </c>
-      <c r="C5" s="19">
-        <v>6</v>
-      </c>
-      <c r="D5" s="19">
-        <v>8</v>
-      </c>
-      <c r="E5" s="19">
-        <v>2</v>
-      </c>
-      <c r="F5" s="19">
-        <v>1</v>
-      </c>
-      <c r="G5" s="19">
-        <v>5</v>
-      </c>
-      <c r="H5" s="19">
-        <v>4</v>
-      </c>
-      <c r="I5" s="19">
-        <v>5004</v>
+      <c r="H5" s="20">
+        <v>24</v>
+      </c>
+      <c r="I5" s="20">
+        <v>17024</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <v>17</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <v>9</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>4</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>3</v>
       </c>
-      <c r="F6" s="19">
-        <v>1</v>
-      </c>
-      <c r="G6" s="19">
+      <c r="F6" s="20">
+        <v>1</v>
+      </c>
+      <c r="G6" s="20">
         <v>18</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <v>21</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="20">
         <v>18021</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="19">
-        <v>16</v>
-      </c>
-      <c r="C7" s="19">
-        <v>4</v>
-      </c>
-      <c r="D7" s="19">
-        <v>9</v>
-      </c>
-      <c r="E7" s="19">
+        <v>55</v>
+      </c>
+      <c r="B7" s="20">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20">
+        <v>6</v>
+      </c>
+      <c r="D7" s="20">
+        <v>8</v>
+      </c>
+      <c r="E7" s="20">
         <v>2</v>
       </c>
-      <c r="F7" s="19">
-        <v>1</v>
-      </c>
-      <c r="G7" s="19">
-        <v>11</v>
-      </c>
-      <c r="H7" s="19">
-        <v>10</v>
-      </c>
-      <c r="I7" s="19">
-        <v>11010</v>
+      <c r="F7" s="20">
+        <v>1</v>
+      </c>
+      <c r="G7" s="20">
+        <v>18</v>
+      </c>
+      <c r="H7" s="20">
+        <v>14</v>
+      </c>
+      <c r="I7" s="20">
+        <v>18014</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="19">
-        <v>16</v>
-      </c>
-      <c r="C8" s="19">
-        <v>6</v>
-      </c>
-      <c r="D8" s="19">
-        <v>7</v>
-      </c>
-      <c r="E8" s="19">
+        <v>57</v>
+      </c>
+      <c r="B8" s="20">
+        <v>17</v>
+      </c>
+      <c r="C8" s="20">
+        <v>5</v>
+      </c>
+      <c r="D8" s="20">
+        <v>9</v>
+      </c>
+      <c r="E8" s="20">
         <v>2</v>
       </c>
-      <c r="F8" s="19">
-        <v>1</v>
-      </c>
-      <c r="G8" s="19">
-        <v>17</v>
-      </c>
-      <c r="H8" s="19">
-        <v>13</v>
-      </c>
-      <c r="I8" s="19">
-        <v>17013</v>
+      <c r="F8" s="20">
+        <v>1</v>
+      </c>
+      <c r="G8" s="20">
+        <v>11</v>
+      </c>
+      <c r="H8" s="20">
+        <v>11</v>
+      </c>
+      <c r="I8" s="20">
+        <v>11011</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="19">
-        <v>15</v>
-      </c>
-      <c r="C9" s="19">
+        <v>53</v>
+      </c>
+      <c r="B9" s="20">
+        <v>16</v>
+      </c>
+      <c r="C9" s="20">
+        <v>7</v>
+      </c>
+      <c r="D9" s="20">
         <v>5</v>
       </c>
-      <c r="D9" s="19">
-        <v>7</v>
-      </c>
-      <c r="E9" s="19">
-        <v>2</v>
-      </c>
-      <c r="F9" s="19">
-        <v>1</v>
-      </c>
-      <c r="G9" s="19">
-        <v>18</v>
-      </c>
-      <c r="H9" s="19">
-        <v>7</v>
-      </c>
-      <c r="I9" s="19">
-        <v>18007</v>
+      <c r="E9" s="20">
+        <v>3</v>
+      </c>
+      <c r="F9" s="20">
+        <v>1</v>
+      </c>
+      <c r="G9" s="20">
+        <v>4</v>
+      </c>
+      <c r="H9" s="20">
+        <v>8</v>
+      </c>
+      <c r="I9" s="20">
+        <v>4008</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="19">
+        <v>43</v>
+      </c>
+      <c r="B10" s="20">
         <v>15</v>
       </c>
-      <c r="C10" s="19">
-        <v>7</v>
-      </c>
-      <c r="D10" s="19">
-        <v>4</v>
-      </c>
-      <c r="E10" s="19">
+      <c r="C10" s="20">
+        <v>6</v>
+      </c>
+      <c r="D10" s="20">
+        <v>5</v>
+      </c>
+      <c r="E10" s="20">
         <v>3</v>
       </c>
-      <c r="F10" s="19">
-        <v>1</v>
-      </c>
-      <c r="G10" s="19">
-        <v>4</v>
-      </c>
-      <c r="H10" s="19">
-        <v>7</v>
-      </c>
-      <c r="I10" s="19">
-        <v>4007</v>
+      <c r="F10" s="20">
+        <v>1</v>
+      </c>
+      <c r="G10" s="20">
+        <v>11</v>
+      </c>
+      <c r="H10" s="20">
+        <v>5</v>
+      </c>
+      <c r="I10" s="20">
+        <v>11005</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="19">
+        <v>33</v>
+      </c>
+      <c r="B11" s="20">
         <v>15</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <v>6</v>
       </c>
-      <c r="D11" s="19">
-        <v>5</v>
-      </c>
-      <c r="E11" s="19">
-        <v>3</v>
-      </c>
-      <c r="F11" s="19">
-        <v>1</v>
-      </c>
-      <c r="G11" s="19">
+      <c r="D11" s="20">
+        <v>6</v>
+      </c>
+      <c r="E11" s="20">
+        <v>2</v>
+      </c>
+      <c r="F11" s="20">
+        <v>1</v>
+      </c>
+      <c r="G11" s="20">
         <v>11</v>
       </c>
-      <c r="H11" s="19">
-        <v>5</v>
-      </c>
-      <c r="I11" s="19">
-        <v>11005</v>
+      <c r="H11" s="20">
+        <v>10</v>
+      </c>
+      <c r="I11" s="20">
+        <v>11010</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="19">
-        <v>14</v>
-      </c>
-      <c r="C12" s="19">
+        <v>42</v>
+      </c>
+      <c r="B12" s="20">
+        <v>15</v>
+      </c>
+      <c r="C12" s="20">
         <v>5</v>
       </c>
-      <c r="D12" s="19">
-        <v>6</v>
-      </c>
-      <c r="E12" s="19">
+      <c r="D12" s="20">
+        <v>7</v>
+      </c>
+      <c r="E12" s="20">
         <v>2</v>
       </c>
-      <c r="F12" s="19">
-        <v>1</v>
-      </c>
-      <c r="G12" s="19">
-        <v>11</v>
-      </c>
-      <c r="H12" s="19">
-        <v>10</v>
-      </c>
-      <c r="I12" s="19">
-        <v>11010</v>
+      <c r="F12" s="20">
+        <v>1</v>
+      </c>
+      <c r="G12" s="20">
+        <v>18</v>
+      </c>
+      <c r="H12" s="20">
+        <v>7</v>
+      </c>
+      <c r="I12" s="20">
+        <v>18007</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="19">
-        <v>13</v>
-      </c>
-      <c r="C13" s="19">
+      <c r="B13" s="20">
+        <v>14</v>
+      </c>
+      <c r="C13" s="20">
         <v>7</v>
       </c>
-      <c r="D13" s="19">
-        <v>4</v>
-      </c>
-      <c r="E13" s="19">
-        <v>1</v>
-      </c>
-      <c r="F13" s="19">
-        <v>1</v>
-      </c>
-      <c r="G13" s="19">
+      <c r="D13" s="20">
+        <v>5</v>
+      </c>
+      <c r="E13" s="20">
+        <v>1</v>
+      </c>
+      <c r="F13" s="20">
+        <v>1</v>
+      </c>
+      <c r="G13" s="20">
         <v>15</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="20">
         <v>6</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="20">
         <v>15006</v>
       </c>
     </row>
@@ -15484,28 +16126,28 @@
       <c r="A14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="19">
-        <v>12</v>
-      </c>
-      <c r="C14" s="19">
+      <c r="B14" s="20">
+        <v>13</v>
+      </c>
+      <c r="C14" s="20">
         <v>6</v>
       </c>
-      <c r="D14" s="19">
-        <v>2</v>
-      </c>
-      <c r="E14" s="19">
+      <c r="D14" s="20">
         <v>3</v>
       </c>
-      <c r="F14" s="19">
-        <v>1</v>
-      </c>
-      <c r="G14" s="19">
+      <c r="E14" s="20">
+        <v>3</v>
+      </c>
+      <c r="F14" s="20">
+        <v>1</v>
+      </c>
+      <c r="G14" s="20">
         <v>5</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="20">
         <v>5</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="20">
         <v>5005</v>
       </c>
     </row>
@@ -15513,28 +16155,28 @@
       <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="19">
-        <v>11</v>
-      </c>
-      <c r="C15" s="19">
-        <v>3</v>
-      </c>
-      <c r="D15" s="19">
+      <c r="B15" s="20">
+        <v>12</v>
+      </c>
+      <c r="C15" s="20">
+        <v>4</v>
+      </c>
+      <c r="D15" s="20">
         <v>6</v>
       </c>
-      <c r="E15" s="19">
-        <v>1</v>
-      </c>
-      <c r="F15" s="19">
-        <v>1</v>
-      </c>
-      <c r="G15" s="19">
-        <v>1</v>
-      </c>
-      <c r="H15" s="19">
+      <c r="E15" s="20">
+        <v>1</v>
+      </c>
+      <c r="F15" s="20">
+        <v>1</v>
+      </c>
+      <c r="G15" s="20">
+        <v>1</v>
+      </c>
+      <c r="H15" s="20">
         <v>2</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="20">
         <v>1002</v>
       </c>
     </row>
@@ -15542,57 +16184,57 @@
       <c r="A16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="19">
-        <v>10</v>
-      </c>
-      <c r="C16" s="19">
+      <c r="B16" s="20">
+        <v>11</v>
+      </c>
+      <c r="C16" s="20">
+        <v>5</v>
+      </c>
+      <c r="D16" s="20">
         <v>4</v>
       </c>
-      <c r="D16" s="19">
-        <v>4</v>
-      </c>
-      <c r="E16" s="19">
-        <v>1</v>
-      </c>
-      <c r="F16" s="19">
-        <v>1</v>
-      </c>
-      <c r="G16" s="19">
-        <v>30</v>
-      </c>
-      <c r="H16" s="19">
+      <c r="E16" s="20">
+        <v>1</v>
+      </c>
+      <c r="F16" s="20">
+        <v>1</v>
+      </c>
+      <c r="G16" s="20">
+        <v>33</v>
+      </c>
+      <c r="H16" s="20">
         <v>11</v>
       </c>
-      <c r="I16" s="19">
-        <v>30011</v>
+      <c r="I16" s="20">
+        <v>33011</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="19">
-        <v>9</v>
-      </c>
-      <c r="C17" s="19">
+      <c r="B17" s="20">
+        <v>10</v>
+      </c>
+      <c r="C17" s="20">
+        <v>3</v>
+      </c>
+      <c r="D17" s="20">
+        <v>5</v>
+      </c>
+      <c r="E17" s="20">
         <v>2</v>
       </c>
-      <c r="D17" s="19">
-        <v>5</v>
-      </c>
-      <c r="E17" s="19">
+      <c r="F17" s="20">
+        <v>0</v>
+      </c>
+      <c r="G17" s="20">
         <v>2</v>
       </c>
-      <c r="F17" s="19">
-        <v>0</v>
-      </c>
-      <c r="G17" s="19">
-        <v>2</v>
-      </c>
-      <c r="H17" s="19">
+      <c r="H17" s="20">
         <v>4</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="20">
         <v>2004</v>
       </c>
     </row>
@@ -15600,202 +16242,202 @@
       <c r="A18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
+        <v>9</v>
+      </c>
+      <c r="C18" s="20">
+        <v>1</v>
+      </c>
+      <c r="D18" s="20">
+        <v>6</v>
+      </c>
+      <c r="E18" s="20">
+        <v>1</v>
+      </c>
+      <c r="F18" s="20">
+        <v>1</v>
+      </c>
+      <c r="G18" s="20">
         <v>8</v>
       </c>
-      <c r="C18" s="19">
-        <v>1</v>
-      </c>
-      <c r="D18" s="19">
+      <c r="H18" s="20">
         <v>5</v>
       </c>
-      <c r="E18" s="19">
-        <v>1</v>
-      </c>
-      <c r="F18" s="19">
-        <v>1</v>
-      </c>
-      <c r="G18" s="19">
-        <v>8</v>
-      </c>
-      <c r="H18" s="19">
-        <v>5</v>
-      </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <v>8005</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="19">
+        <v>58</v>
+      </c>
+      <c r="B19" s="20">
         <v>7</v>
       </c>
-      <c r="C19" s="19">
-        <v>2</v>
-      </c>
-      <c r="D19" s="19">
+      <c r="C19" s="20">
+        <v>1</v>
+      </c>
+      <c r="D19" s="20">
+        <v>4</v>
+      </c>
+      <c r="E19" s="20">
+        <v>1</v>
+      </c>
+      <c r="F19" s="20">
+        <v>1</v>
+      </c>
+      <c r="G19" s="20">
+        <v>5</v>
+      </c>
+      <c r="H19" s="20">
         <v>3</v>
       </c>
-      <c r="E19" s="19">
-        <v>1</v>
-      </c>
-      <c r="F19" s="19">
-        <v>1</v>
-      </c>
-      <c r="G19" s="19">
-        <v>13</v>
-      </c>
-      <c r="H19" s="19">
-        <v>7</v>
-      </c>
-      <c r="I19" s="19">
-        <v>13007</v>
+      <c r="I19" s="20">
+        <v>5003</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="19">
+        <v>64</v>
+      </c>
+      <c r="B20" s="20">
         <v>7</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <v>2</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <v>3</v>
       </c>
-      <c r="E20" s="19">
-        <v>2</v>
-      </c>
-      <c r="F20" s="19">
-        <v>0</v>
-      </c>
-      <c r="G20" s="19">
-        <v>3</v>
-      </c>
-      <c r="H20" s="19">
-        <v>2</v>
-      </c>
-      <c r="I20" s="19">
-        <v>3002</v>
+      <c r="E20" s="20">
+        <v>1</v>
+      </c>
+      <c r="F20" s="20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="20">
+        <v>13</v>
+      </c>
+      <c r="H20" s="20">
+        <v>7</v>
+      </c>
+      <c r="I20" s="20">
+        <v>13007</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="19">
+        <v>46</v>
+      </c>
+      <c r="B21" s="20">
         <v>7</v>
       </c>
-      <c r="C21" s="19">
-        <v>4</v>
-      </c>
-      <c r="D21" s="19">
-        <v>1</v>
-      </c>
-      <c r="E21" s="19">
-        <v>1</v>
-      </c>
-      <c r="F21" s="19">
-        <v>1</v>
-      </c>
-      <c r="G21" s="19">
-        <v>4</v>
-      </c>
-      <c r="H21" s="19">
+      <c r="C21" s="20">
+        <v>2</v>
+      </c>
+      <c r="D21" s="20">
         <v>3</v>
       </c>
-      <c r="I21" s="19">
-        <v>4003</v>
+      <c r="E21" s="20">
+        <v>2</v>
+      </c>
+      <c r="F21" s="20">
+        <v>0</v>
+      </c>
+      <c r="G21" s="20">
+        <v>3</v>
+      </c>
+      <c r="H21" s="20">
+        <v>2</v>
+      </c>
+      <c r="I21" s="20">
+        <v>3002</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="19">
-        <v>6</v>
-      </c>
-      <c r="C22" s="19">
+        <v>26</v>
+      </c>
+      <c r="B22" s="20">
+        <v>7</v>
+      </c>
+      <c r="C22" s="20">
         <v>4</v>
       </c>
-      <c r="D22" s="19">
-        <v>0</v>
-      </c>
-      <c r="E22" s="19">
-        <v>1</v>
-      </c>
-      <c r="F22" s="19">
-        <v>1</v>
-      </c>
-      <c r="G22" s="19">
-        <v>5</v>
-      </c>
-      <c r="H22" s="19">
-        <v>0</v>
-      </c>
-      <c r="I22" s="19">
-        <v>5000</v>
+      <c r="D22" s="20">
+        <v>1</v>
+      </c>
+      <c r="E22" s="20">
+        <v>1</v>
+      </c>
+      <c r="F22" s="20">
+        <v>1</v>
+      </c>
+      <c r="G22" s="20">
+        <v>4</v>
+      </c>
+      <c r="H22" s="20">
+        <v>3</v>
+      </c>
+      <c r="I22" s="20">
+        <v>4003</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" s="19">
+        <v>28</v>
+      </c>
+      <c r="B23" s="20">
         <v>6</v>
       </c>
-      <c r="C23" s="19">
-        <v>1</v>
-      </c>
-      <c r="D23" s="19">
-        <v>3</v>
-      </c>
-      <c r="E23" s="19">
-        <v>1</v>
-      </c>
-      <c r="F23" s="19">
-        <v>1</v>
-      </c>
-      <c r="G23" s="19">
+      <c r="C23" s="20">
         <v>4</v>
       </c>
-      <c r="H23" s="19">
-        <v>3</v>
-      </c>
-      <c r="I23" s="19">
-        <v>4003</v>
+      <c r="D23" s="20">
+        <v>0</v>
+      </c>
+      <c r="E23" s="20">
+        <v>1</v>
+      </c>
+      <c r="F23" s="20">
+        <v>1</v>
+      </c>
+      <c r="G23" s="20">
+        <v>5</v>
+      </c>
+      <c r="H23" s="20">
+        <v>0</v>
+      </c>
+      <c r="I23" s="20">
+        <v>5000</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="20">
         <v>5</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="20">
         <v>2</v>
       </c>
-      <c r="D24" s="19">
-        <v>1</v>
-      </c>
-      <c r="E24" s="19">
+      <c r="D24" s="20">
+        <v>1</v>
+      </c>
+      <c r="E24" s="20">
         <v>2</v>
       </c>
-      <c r="F24" s="19">
-        <v>0</v>
-      </c>
-      <c r="G24" s="19">
-        <v>0</v>
-      </c>
-      <c r="H24" s="19">
-        <v>0</v>
-      </c>
-      <c r="I24" s="19">
+      <c r="F24" s="20">
+        <v>0</v>
+      </c>
+      <c r="G24" s="20">
+        <v>0</v>
+      </c>
+      <c r="H24" s="20">
+        <v>0</v>
+      </c>
+      <c r="I24" s="20">
         <v>0</v>
       </c>
     </row>
@@ -15803,231 +16445,231 @@
       <c r="A25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="20">
         <v>5</v>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="20">
         <v>3</v>
       </c>
-      <c r="D25" s="19">
-        <v>1</v>
-      </c>
-      <c r="E25" s="19">
-        <v>0</v>
-      </c>
-      <c r="F25" s="19">
-        <v>1</v>
-      </c>
-      <c r="G25" s="19">
+      <c r="D25" s="20">
+        <v>1</v>
+      </c>
+      <c r="E25" s="20">
+        <v>0</v>
+      </c>
+      <c r="F25" s="20">
+        <v>1</v>
+      </c>
+      <c r="G25" s="20">
         <v>5</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="20">
         <v>2</v>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="20">
         <v>5002</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="19">
+        <v>60</v>
+      </c>
+      <c r="B26" s="20">
+        <v>4</v>
+      </c>
+      <c r="C26" s="20">
         <v>3</v>
       </c>
-      <c r="C26" s="19">
-        <v>1</v>
-      </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
+        <v>1</v>
+      </c>
+      <c r="E26" s="20">
+        <v>0</v>
+      </c>
+      <c r="F26" s="20">
+        <v>0</v>
+      </c>
+      <c r="G26" s="20">
         <v>2</v>
       </c>
-      <c r="E26" s="19">
-        <v>0</v>
-      </c>
-      <c r="F26" s="19">
-        <v>0</v>
-      </c>
-      <c r="G26" s="19">
-        <v>2</v>
-      </c>
-      <c r="H26" s="19">
-        <v>1</v>
-      </c>
-      <c r="I26" s="19">
-        <v>2001</v>
+      <c r="H26" s="20">
+        <v>3</v>
+      </c>
+      <c r="I26" s="20">
+        <v>2003</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="20">
         <v>3</v>
       </c>
-      <c r="C27" s="19">
-        <v>1</v>
-      </c>
-      <c r="D27" s="19">
-        <v>1</v>
-      </c>
-      <c r="E27" s="19">
-        <v>0</v>
-      </c>
-      <c r="F27" s="19">
-        <v>1</v>
-      </c>
-      <c r="G27" s="19">
-        <v>0</v>
-      </c>
-      <c r="H27" s="19">
-        <v>0</v>
-      </c>
-      <c r="I27" s="19">
+      <c r="C27" s="20">
+        <v>1</v>
+      </c>
+      <c r="D27" s="20">
+        <v>1</v>
+      </c>
+      <c r="E27" s="20">
+        <v>0</v>
+      </c>
+      <c r="F27" s="20">
+        <v>1</v>
+      </c>
+      <c r="G27" s="20">
+        <v>0</v>
+      </c>
+      <c r="H27" s="20">
+        <v>0</v>
+      </c>
+      <c r="I27" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="19">
+        <v>52</v>
+      </c>
+      <c r="B28" s="20">
         <v>3</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
+        <v>1</v>
+      </c>
+      <c r="D28" s="20">
         <v>2</v>
       </c>
-      <c r="D28" s="19">
-        <v>1</v>
-      </c>
-      <c r="E28" s="19">
-        <v>0</v>
-      </c>
-      <c r="F28" s="19">
-        <v>0</v>
-      </c>
-      <c r="G28" s="19">
+      <c r="E28" s="20">
+        <v>0</v>
+      </c>
+      <c r="F28" s="20">
+        <v>0</v>
+      </c>
+      <c r="G28" s="20">
         <v>2</v>
       </c>
-      <c r="H28" s="19">
-        <v>2</v>
-      </c>
-      <c r="I28" s="19">
-        <v>2002</v>
+      <c r="H28" s="20">
+        <v>1</v>
+      </c>
+      <c r="I28" s="20">
+        <v>2001</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="19">
+        <v>93</v>
+      </c>
+      <c r="B29" s="20">
+        <v>3</v>
+      </c>
+      <c r="C29" s="20">
+        <v>1</v>
+      </c>
+      <c r="D29" s="20">
         <v>2</v>
       </c>
-      <c r="C29" s="19">
-        <v>0</v>
-      </c>
-      <c r="D29" s="19">
-        <v>1</v>
-      </c>
-      <c r="E29" s="19">
-        <v>1</v>
-      </c>
-      <c r="F29" s="19">
-        <v>0</v>
-      </c>
-      <c r="G29" s="19">
-        <v>1</v>
-      </c>
-      <c r="H29" s="19">
-        <v>0</v>
-      </c>
-      <c r="I29" s="19">
-        <v>1000</v>
+      <c r="E29" s="20">
+        <v>0</v>
+      </c>
+      <c r="F29" s="20">
+        <v>0</v>
+      </c>
+      <c r="G29" s="20">
+        <v>0</v>
+      </c>
+      <c r="H29" s="20">
+        <v>0</v>
+      </c>
+      <c r="I29" s="20">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="19">
+        <v>6</v>
+      </c>
+      <c r="B30" s="20">
         <v>2</v>
       </c>
-      <c r="C30" s="19">
-        <v>1</v>
-      </c>
-      <c r="D30" s="19">
-        <v>1</v>
-      </c>
-      <c r="E30" s="19">
-        <v>0</v>
-      </c>
-      <c r="F30" s="19">
-        <v>0</v>
-      </c>
-      <c r="G30" s="19">
-        <v>1</v>
-      </c>
-      <c r="H30" s="19">
-        <v>0</v>
-      </c>
-      <c r="I30" s="19">
+      <c r="C30" s="20">
+        <v>0</v>
+      </c>
+      <c r="D30" s="20">
+        <v>1</v>
+      </c>
+      <c r="E30" s="20">
+        <v>1</v>
+      </c>
+      <c r="F30" s="20">
+        <v>0</v>
+      </c>
+      <c r="G30" s="20">
+        <v>1</v>
+      </c>
+      <c r="H30" s="20">
+        <v>0</v>
+      </c>
+      <c r="I30" s="20">
         <v>1000</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="19">
+        <v>7</v>
+      </c>
+      <c r="B31" s="20">
         <v>2</v>
       </c>
-      <c r="C31" s="19">
-        <v>1</v>
-      </c>
-      <c r="D31" s="19">
-        <v>1</v>
-      </c>
-      <c r="E31" s="19">
-        <v>0</v>
-      </c>
-      <c r="F31" s="19">
-        <v>0</v>
-      </c>
-      <c r="G31" s="19">
-        <v>0</v>
-      </c>
-      <c r="H31" s="19">
-        <v>0</v>
-      </c>
-      <c r="I31" s="19">
-        <v>0</v>
+      <c r="C31" s="20">
+        <v>1</v>
+      </c>
+      <c r="D31" s="20">
+        <v>1</v>
+      </c>
+      <c r="E31" s="20">
+        <v>0</v>
+      </c>
+      <c r="F31" s="20">
+        <v>0</v>
+      </c>
+      <c r="G31" s="20">
+        <v>1</v>
+      </c>
+      <c r="H31" s="20">
+        <v>0</v>
+      </c>
+      <c r="I31" s="20">
+        <v>1000</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="20">
         <v>2</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="20">
         <v>2</v>
       </c>
-      <c r="D32" s="19">
-        <v>0</v>
-      </c>
-      <c r="E32" s="19">
-        <v>0</v>
-      </c>
-      <c r="F32" s="19">
-        <v>0</v>
-      </c>
-      <c r="G32" s="19">
+      <c r="D32" s="20">
+        <v>0</v>
+      </c>
+      <c r="E32" s="20">
+        <v>0</v>
+      </c>
+      <c r="F32" s="20">
+        <v>0</v>
+      </c>
+      <c r="G32" s="20">
         <v>2</v>
       </c>
-      <c r="H32" s="19">
-        <v>1</v>
-      </c>
-      <c r="I32" s="19">
+      <c r="H32" s="20">
+        <v>1</v>
+      </c>
+      <c r="I32" s="20">
         <v>2001</v>
       </c>
     </row>
@@ -16035,28 +16677,28 @@
       <c r="A33" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="19">
-        <v>1</v>
-      </c>
-      <c r="C33" s="19">
-        <v>0</v>
-      </c>
-      <c r="D33" s="19">
-        <v>1</v>
-      </c>
-      <c r="E33" s="19">
-        <v>0</v>
-      </c>
-      <c r="F33" s="19">
-        <v>0</v>
-      </c>
-      <c r="G33" s="19">
-        <v>1</v>
-      </c>
-      <c r="H33" s="19">
-        <v>0</v>
-      </c>
-      <c r="I33" s="19">
+      <c r="B33" s="20">
+        <v>1</v>
+      </c>
+      <c r="C33" s="20">
+        <v>0</v>
+      </c>
+      <c r="D33" s="20">
+        <v>1</v>
+      </c>
+      <c r="E33" s="20">
+        <v>0</v>
+      </c>
+      <c r="F33" s="20">
+        <v>0</v>
+      </c>
+      <c r="G33" s="20">
+        <v>1</v>
+      </c>
+      <c r="H33" s="20">
+        <v>0</v>
+      </c>
+      <c r="I33" s="20">
         <v>1000</v>
       </c>
     </row>
@@ -16064,28 +16706,28 @@
       <c r="A34" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="19">
-        <v>1</v>
-      </c>
-      <c r="C34" s="19">
-        <v>0</v>
-      </c>
-      <c r="D34" s="19">
-        <v>1</v>
-      </c>
-      <c r="E34" s="19">
-        <v>0</v>
-      </c>
-      <c r="F34" s="19">
-        <v>0</v>
-      </c>
-      <c r="G34" s="19">
-        <v>1</v>
-      </c>
-      <c r="H34" s="19">
-        <v>1</v>
-      </c>
-      <c r="I34" s="19">
+      <c r="B34" s="20">
+        <v>1</v>
+      </c>
+      <c r="C34" s="20">
+        <v>0</v>
+      </c>
+      <c r="D34" s="20">
+        <v>1</v>
+      </c>
+      <c r="E34" s="20">
+        <v>0</v>
+      </c>
+      <c r="F34" s="20">
+        <v>0</v>
+      </c>
+      <c r="G34" s="20">
+        <v>1</v>
+      </c>
+      <c r="H34" s="20">
+        <v>1</v>
+      </c>
+      <c r="I34" s="20">
         <v>1001</v>
       </c>
     </row>
@@ -16093,28 +16735,28 @@
       <c r="A35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="19">
-        <v>1</v>
-      </c>
-      <c r="C35" s="19">
-        <v>0</v>
-      </c>
-      <c r="D35" s="19">
-        <v>1</v>
-      </c>
-      <c r="E35" s="19">
-        <v>0</v>
-      </c>
-      <c r="F35" s="19">
-        <v>0</v>
-      </c>
-      <c r="G35" s="19">
-        <v>0</v>
-      </c>
-      <c r="H35" s="19">
-        <v>0</v>
-      </c>
-      <c r="I35" s="19">
+      <c r="B35" s="20">
+        <v>1</v>
+      </c>
+      <c r="C35" s="20">
+        <v>0</v>
+      </c>
+      <c r="D35" s="20">
+        <v>1</v>
+      </c>
+      <c r="E35" s="20">
+        <v>0</v>
+      </c>
+      <c r="F35" s="20">
+        <v>0</v>
+      </c>
+      <c r="G35" s="20">
+        <v>0</v>
+      </c>
+      <c r="H35" s="20">
+        <v>0</v>
+      </c>
+      <c r="I35" s="20">
         <v>0</v>
       </c>
     </row>
@@ -16122,28 +16764,28 @@
       <c r="A36" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="19">
-        <v>1</v>
-      </c>
-      <c r="C36" s="19">
-        <v>1</v>
-      </c>
-      <c r="D36" s="19">
-        <v>0</v>
-      </c>
-      <c r="E36" s="19">
-        <v>0</v>
-      </c>
-      <c r="F36" s="19">
-        <v>0</v>
-      </c>
-      <c r="G36" s="19">
+      <c r="B36" s="20">
+        <v>1</v>
+      </c>
+      <c r="C36" s="20">
+        <v>1</v>
+      </c>
+      <c r="D36" s="20">
+        <v>0</v>
+      </c>
+      <c r="E36" s="20">
+        <v>0</v>
+      </c>
+      <c r="F36" s="20">
+        <v>0</v>
+      </c>
+      <c r="G36" s="20">
         <v>2</v>
       </c>
-      <c r="H36" s="19">
-        <v>0</v>
-      </c>
-      <c r="I36" s="19">
+      <c r="H36" s="20">
+        <v>0</v>
+      </c>
+      <c r="I36" s="20">
         <v>2000</v>
       </c>
     </row>
@@ -16151,29 +16793,29 @@
       <c r="A37" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="19">
-        <v>270</v>
-      </c>
-      <c r="C37" s="19">
-        <v>105</v>
-      </c>
-      <c r="D37" s="19">
-        <v>105</v>
-      </c>
-      <c r="E37" s="19">
+      <c r="B37" s="20">
+        <v>284</v>
+      </c>
+      <c r="C37" s="20">
+        <v>112</v>
+      </c>
+      <c r="D37" s="20">
+        <v>112</v>
+      </c>
+      <c r="E37" s="20">
         <v>40</v>
       </c>
-      <c r="F37" s="19">
+      <c r="F37" s="20">
         <v>20</v>
       </c>
-      <c r="G37" s="19">
-        <v>219</v>
-      </c>
-      <c r="H37" s="19">
-        <v>156</v>
-      </c>
-      <c r="I37" s="19">
-        <v>219156</v>
+      <c r="G37" s="20">
+        <v>224</v>
+      </c>
+      <c r="H37" s="20">
+        <v>161</v>
+      </c>
+      <c r="I37" s="20">
+        <v>224161</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -16220,10 +16862,10 @@
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.140625" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -16244,83 +16886,83 @@
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="19">
-        <v>30</v>
-      </c>
-      <c r="C2" s="19">
+      <c r="B2" s="20">
+        <v>33</v>
+      </c>
+      <c r="C2" s="20">
         <v>11</v>
       </c>
-      <c r="D2" s="19">
-        <v>30011</v>
+      <c r="D2" s="20">
+        <v>33011</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="20">
         <v>18</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="20">
         <v>21</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="20">
         <v>18021</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="19">
+        <v>55</v>
+      </c>
+      <c r="B4" s="20">
         <v>18</v>
       </c>
-      <c r="C4" s="19">
-        <v>7</v>
-      </c>
-      <c r="D4" s="19">
-        <v>18007</v>
+      <c r="C4" s="20">
+        <v>14</v>
+      </c>
+      <c r="D4" s="20">
+        <v>18014</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="19">
-        <v>17</v>
-      </c>
-      <c r="C5" s="19">
-        <v>24</v>
-      </c>
-      <c r="D5" s="19">
-        <v>17024</v>
+        <v>42</v>
+      </c>
+      <c r="B5" s="20">
+        <v>18</v>
+      </c>
+      <c r="C5" s="20">
+        <v>7</v>
+      </c>
+      <c r="D5" s="20">
+        <v>18007</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="19">
+        <v>40</v>
+      </c>
+      <c r="B6" s="20">
         <v>17</v>
       </c>
-      <c r="C6" s="19">
-        <v>13</v>
-      </c>
-      <c r="D6" s="19">
-        <v>17013</v>
+      <c r="C6" s="20">
+        <v>24</v>
+      </c>
+      <c r="D6" s="20">
+        <v>17024</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <v>15</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <v>6</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <v>15006</v>
       </c>
     </row>
@@ -16328,41 +16970,41 @@
       <c r="A8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <v>13</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <v>7</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <v>13007</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="19">
+        <v>57</v>
+      </c>
+      <c r="B9" s="20">
         <v>11</v>
       </c>
-      <c r="C9" s="19">
-        <v>10</v>
-      </c>
-      <c r="D9" s="19">
-        <v>11010</v>
+      <c r="C9" s="20">
+        <v>11</v>
+      </c>
+      <c r="D9" s="20">
+        <v>11011</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="19">
+        <v>33</v>
+      </c>
+      <c r="B10" s="20">
         <v>11</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <v>10</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <v>11010</v>
       </c>
     </row>
@@ -16370,13 +17012,13 @@
       <c r="A11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="20">
         <v>11</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <v>5</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <v>11005</v>
       </c>
     </row>
@@ -16384,13 +17026,13 @@
       <c r="A12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <v>8</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <v>5</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <v>8005</v>
       </c>
     </row>
@@ -16398,13 +17040,13 @@
       <c r="A13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <v>5</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <v>5</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <v>5005</v>
       </c>
     </row>
@@ -16412,83 +17054,83 @@
       <c r="A14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <v>5</v>
       </c>
-      <c r="C14" s="19">
-        <v>4</v>
-      </c>
-      <c r="D14" s="19">
-        <v>5004</v>
+      <c r="C14" s="20">
+        <v>5</v>
+      </c>
+      <c r="D14" s="20">
+        <v>5005</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="19">
+        <v>58</v>
+      </c>
+      <c r="B15" s="20">
         <v>5</v>
       </c>
-      <c r="C15" s="19">
-        <v>2</v>
-      </c>
-      <c r="D15" s="19">
-        <v>5002</v>
+      <c r="C15" s="20">
+        <v>3</v>
+      </c>
+      <c r="D15" s="20">
+        <v>5003</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="19">
+        <v>34</v>
+      </c>
+      <c r="B16" s="20">
         <v>5</v>
       </c>
-      <c r="C16" s="19">
-        <v>0</v>
-      </c>
-      <c r="D16" s="19">
-        <v>5000</v>
+      <c r="C16" s="20">
+        <v>2</v>
+      </c>
+      <c r="D16" s="20">
+        <v>5002</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="19">
-        <v>4</v>
-      </c>
-      <c r="C17" s="19">
-        <v>7</v>
-      </c>
-      <c r="D17" s="19">
-        <v>4007</v>
+        <v>28</v>
+      </c>
+      <c r="B17" s="20">
+        <v>5</v>
+      </c>
+      <c r="C17" s="20">
+        <v>0</v>
+      </c>
+      <c r="D17" s="20">
+        <v>5000</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="19">
+        <v>53</v>
+      </c>
+      <c r="B18" s="20">
         <v>4</v>
       </c>
-      <c r="C18" s="19">
-        <v>3</v>
-      </c>
-      <c r="D18" s="19">
-        <v>4003</v>
+      <c r="C18" s="20">
+        <v>8</v>
+      </c>
+      <c r="D18" s="20">
+        <v>4008</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="20">
         <v>4</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="20">
         <v>3</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="20">
         <v>4003</v>
       </c>
     </row>
@@ -16496,13 +17138,13 @@
       <c r="A20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="20">
         <v>3</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <v>2</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <v>3002</v>
       </c>
     </row>
@@ -16510,13 +17152,13 @@
       <c r="A21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <v>2</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <v>4</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <v>2004</v>
       </c>
     </row>
@@ -16524,27 +17166,27 @@
       <c r="A22" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <v>2</v>
       </c>
-      <c r="C22" s="19">
-        <v>2</v>
-      </c>
-      <c r="D22" s="19">
-        <v>2002</v>
+      <c r="C22" s="20">
+        <v>3</v>
+      </c>
+      <c r="D22" s="20">
+        <v>2003</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="20">
         <v>2</v>
       </c>
-      <c r="C23" s="19">
-        <v>1</v>
-      </c>
-      <c r="D23" s="19">
+      <c r="C23" s="20">
+        <v>1</v>
+      </c>
+      <c r="D23" s="20">
         <v>2001</v>
       </c>
     </row>
@@ -16552,13 +17194,13 @@
       <c r="A24" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="20">
         <v>2</v>
       </c>
-      <c r="C24" s="19">
-        <v>1</v>
-      </c>
-      <c r="D24" s="19">
+      <c r="C24" s="20">
+        <v>1</v>
+      </c>
+      <c r="D24" s="20">
         <v>2001</v>
       </c>
     </row>
@@ -16566,13 +17208,13 @@
       <c r="A25" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="20">
         <v>2</v>
       </c>
-      <c r="C25" s="19">
-        <v>0</v>
-      </c>
-      <c r="D25" s="19">
+      <c r="C25" s="20">
+        <v>0</v>
+      </c>
+      <c r="D25" s="20">
         <v>2000</v>
       </c>
     </row>
@@ -16580,13 +17222,13 @@
       <c r="A26" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="19">
-        <v>1</v>
-      </c>
-      <c r="C26" s="19">
+      <c r="B26" s="20">
+        <v>1</v>
+      </c>
+      <c r="C26" s="20">
         <v>2</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <v>1002</v>
       </c>
     </row>
@@ -16594,13 +17236,13 @@
       <c r="A27" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="19">
-        <v>1</v>
-      </c>
-      <c r="C27" s="19">
-        <v>1</v>
-      </c>
-      <c r="D27" s="19">
+      <c r="B27" s="20">
+        <v>1</v>
+      </c>
+      <c r="C27" s="20">
+        <v>1</v>
+      </c>
+      <c r="D27" s="20">
         <v>1001</v>
       </c>
     </row>
@@ -16608,13 +17250,13 @@
       <c r="A28" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B28" s="19">
-        <v>1</v>
-      </c>
-      <c r="C28" s="19">
-        <v>0</v>
-      </c>
-      <c r="D28" s="19">
+      <c r="B28" s="20">
+        <v>1</v>
+      </c>
+      <c r="C28" s="20">
+        <v>0</v>
+      </c>
+      <c r="D28" s="20">
         <v>1000</v>
       </c>
     </row>
@@ -16622,13 +17264,13 @@
       <c r="A29" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="19">
-        <v>1</v>
-      </c>
-      <c r="C29" s="19">
-        <v>0</v>
-      </c>
-      <c r="D29" s="19">
+      <c r="B29" s="20">
+        <v>1</v>
+      </c>
+      <c r="C29" s="20">
+        <v>0</v>
+      </c>
+      <c r="D29" s="20">
         <v>1000</v>
       </c>
     </row>
@@ -16636,13 +17278,13 @@
       <c r="A30" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="19">
-        <v>1</v>
-      </c>
-      <c r="C30" s="19">
-        <v>0</v>
-      </c>
-      <c r="D30" s="19">
+      <c r="B30" s="20">
+        <v>1</v>
+      </c>
+      <c r="C30" s="20">
+        <v>0</v>
+      </c>
+      <c r="D30" s="20">
         <v>1000</v>
       </c>
     </row>
@@ -16650,13 +17292,13 @@
       <c r="A31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="19">
-        <v>0</v>
-      </c>
-      <c r="C31" s="19">
-        <v>0</v>
-      </c>
-      <c r="D31" s="19">
+      <c r="B31" s="20">
+        <v>0</v>
+      </c>
+      <c r="C31" s="20">
+        <v>0</v>
+      </c>
+      <c r="D31" s="20">
         <v>0</v>
       </c>
     </row>
@@ -16664,13 +17306,13 @@
       <c r="A32" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B32" s="19">
-        <v>0</v>
-      </c>
-      <c r="C32" s="19">
-        <v>0</v>
-      </c>
-      <c r="D32" s="19">
+      <c r="B32" s="20">
+        <v>0</v>
+      </c>
+      <c r="C32" s="20">
+        <v>0</v>
+      </c>
+      <c r="D32" s="20">
         <v>0</v>
       </c>
     </row>
@@ -16678,13 +17320,13 @@
       <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="19">
-        <v>0</v>
-      </c>
-      <c r="C33" s="19">
-        <v>0</v>
-      </c>
-      <c r="D33" s="19">
+      <c r="B33" s="20">
+        <v>0</v>
+      </c>
+      <c r="C33" s="20">
+        <v>0</v>
+      </c>
+      <c r="D33" s="20">
         <v>0</v>
       </c>
     </row>
@@ -16692,13 +17334,13 @@
       <c r="A34" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="19">
-        <v>0</v>
-      </c>
-      <c r="C34" s="19">
-        <v>0</v>
-      </c>
-      <c r="D34" s="19">
+      <c r="B34" s="20">
+        <v>0</v>
+      </c>
+      <c r="C34" s="20">
+        <v>0</v>
+      </c>
+      <c r="D34" s="20">
         <v>0</v>
       </c>
     </row>
@@ -16706,14 +17348,14 @@
       <c r="A35" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="19">
-        <v>219</v>
-      </c>
-      <c r="C35" s="19">
-        <v>156</v>
-      </c>
-      <c r="D35" s="19">
-        <v>219156</v>
+      <c r="B35" s="20">
+        <v>224</v>
+      </c>
+      <c r="C35" s="20">
+        <v>161</v>
+      </c>
+      <c r="D35" s="20">
+        <v>224161</v>
       </c>
     </row>
   </sheetData>
@@ -16801,8 +17443,8 @@
         <v>74</v>
       </c>
       <c r="B5">
-        <f>ROWS(_xlfn.UNIQUE('Player Match Stats'!A2:A271))</f>
-        <v>19</v>
+        <f>ROWS(_xlfn.UNIQUE('Player Match Stats'!A2:A285))</f>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
         <v>75</v>
@@ -16847,32 +17489,32 @@
         <v>97</v>
       </c>
       <c r="L6" t="str" cm="1">
-        <f t="array" ref="L6:T16">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(A8:I39,J8:J39="✅ SIM"),7,-1)</f>
-        <v>marcus</v>
+        <f t="array" ref="L6:T17">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(A8:I39,J8:J39="✅ SIM"),7,-1)</f>
+        <v>guilherme</v>
       </c>
       <c r="M6" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N6" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O6" s="15">
         <v>4</v>
       </c>
       <c r="P6" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="15">
         <v>1</v>
       </c>
       <c r="R6" s="13">
-        <v>0.58333333333333337</v>
+        <v>0.5625</v>
       </c>
       <c r="S6" s="13">
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="T6" s="13">
-        <v>8.3333333333333329E-2</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -16910,37 +17552,37 @@
         <v>98</v>
       </c>
       <c r="L7" t="str">
-        <v>guilherme</v>
+        <v>marcus</v>
       </c>
       <c r="M7" s="15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N7" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O7" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P7" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="15">
         <v>1</v>
       </c>
       <c r="R7" s="13">
-        <v>0.5625</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="S7" s="13">
-        <v>0.25</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="T7" s="13">
-        <v>0.1875</v>
+        <v>7.6923076923076927E-2</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>Geral!A4</f>
-        <v>douglas b</v>
+        <v>miguel saddi</v>
       </c>
       <c r="B8">
         <f>COUNTIF('Player Match Stats'!$C:$C,A8)</f>
@@ -16952,11 +17594,11 @@
       </c>
       <c r="D8">
         <f>SUMIF('Player Match Stats'!$C:$C,A8,'Player Match Stats'!$G:$G)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <f>SUMIF('Player Match Stats'!$C:$C,A8,'Player Match Stats'!$H:$H)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="15">
         <f>SUMIF('Player Match Stats'!$C:$C,A8,'Player Match Stats'!$I:$I)</f>
@@ -16968,11 +17610,11 @@
       </c>
       <c r="H8" s="13">
         <f t="shared" ref="H8:H39" si="1">IF((C8+D8+E8)=0,0,D8/(C8+D8+E8))</f>
-        <v>0.41176470588235292</v>
+        <v>0.47058823529411764</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" ref="I8:I39" si="2">IF((C8+D8+E8)=0,0,E8/(C8+D8+E8))</f>
-        <v>0.17647058823529413</v>
+        <v>0.11764705882352941</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ref="J8:J39" si="3">IF(B8&gt;=$D$5,"✅ SIM","❌ NÃO")</f>
@@ -16985,13 +17627,13 @@
         <v>leandro</v>
       </c>
       <c r="M8" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N8" s="15">
         <v>6</v>
       </c>
       <c r="O8" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" s="15">
         <v>3</v>
@@ -17000,35 +17642,35 @@
         <v>1</v>
       </c>
       <c r="R8" s="13">
-        <v>0.54545454545454541</v>
+        <v>0.5</v>
       </c>
       <c r="S8" s="13">
-        <v>0.18181818181818182</v>
+        <v>0.25</v>
       </c>
       <c r="T8" s="13">
-        <v>0.27272727272727271</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>Geral!A5</f>
-        <v>miguel saddi</v>
+        <v>douglas b</v>
       </c>
       <c r="B9">
         <f>COUNTIF('Player Match Stats'!$C:$C,A9)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <f>SUMIF('Player Match Stats'!$C:$C,A9,'Player Match Stats'!$F:$F)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <f>SUMIF('Player Match Stats'!$C:$C,A9,'Player Match Stats'!$G:$G)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <f>SUMIF('Player Match Stats'!$C:$C,A9,'Player Match Stats'!$H:$H)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="15">
         <f>SUMIF('Player Match Stats'!$C:$C,A9,'Player Match Stats'!$I:$I)</f>
@@ -17036,15 +17678,15 @@
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>0.375</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="H9" s="13">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="I9" s="13">
         <f t="shared" si="2"/>
-        <v>0.125</v>
+        <v>0.17647058823529413</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" si="3"/>
@@ -17058,13 +17700,13 @@
         <v>lucas volcov</v>
       </c>
       <c r="M9" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N9" s="15">
         <v>7</v>
       </c>
       <c r="O9" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P9" s="15">
         <v>3</v>
@@ -17073,13 +17715,13 @@
         <v>1</v>
       </c>
       <c r="R9" s="13">
-        <v>0.5</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="S9" s="13">
-        <v>0.2857142857142857</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="T9" s="13">
-        <v>0.21428571428571427</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -17158,19 +17800,19 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>Geral!A7</f>
-        <v>diego</v>
+        <v>gabriel diretoria</v>
       </c>
       <c r="B11">
         <f>COUNTIF('Player Match Stats'!$C:$C,A11)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <f>SUMIF('Player Match Stats'!$C:$C,A11,'Player Match Stats'!$F:$F)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <f>SUMIF('Player Match Stats'!$C:$C,A11,'Player Match Stats'!$G:$G)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <f>SUMIF('Player Match Stats'!$C:$C,A11,'Player Match Stats'!$H:$H)</f>
@@ -17182,15 +17824,15 @@
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>0.26666666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="H11" s="13">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="13">
         <f t="shared" si="2"/>
-        <v>0.13333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="J11" s="13" t="str">
         <f t="shared" si="3"/>
@@ -17201,49 +17843,49 @@
         <v>6</v>
       </c>
       <c r="L11" t="str">
-        <v>douglas b</v>
+        <v>joao</v>
       </c>
       <c r="M11" s="15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N11" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O11" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P11" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="15">
         <v>1</v>
       </c>
       <c r="R11" s="13">
-        <v>0.41176470588235292</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S11" s="13">
-        <v>0.41176470588235292</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="T11" s="13">
-        <v>0.17647058823529413</v>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>Geral!A8</f>
-        <v>gabriel diretoria</v>
+        <v>diego</v>
       </c>
       <c r="B12">
         <f>COUNTIF('Player Match Stats'!$C:$C,A12)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <f>SUMIF('Player Match Stats'!$C:$C,A12,'Player Match Stats'!$F:$F)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <f>SUMIF('Player Match Stats'!$C:$C,A12,'Player Match Stats'!$G:$G)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <f>SUMIF('Player Match Stats'!$C:$C,A12,'Player Match Stats'!$H:$H)</f>
@@ -17255,15 +17897,15 @@
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.3125</v>
       </c>
       <c r="H12" s="13">
         <f t="shared" si="1"/>
-        <v>0.46666666666666667</v>
+        <v>0.5625</v>
       </c>
       <c r="I12" s="13">
         <f t="shared" si="2"/>
-        <v>0.13333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="J12" s="13" t="str">
         <f t="shared" si="3"/>
@@ -17274,16 +17916,16 @@
         <v>7</v>
       </c>
       <c r="L12" t="str">
-        <v>gabriel diretoria</v>
+        <v>miguel saddi</v>
       </c>
       <c r="M12" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N12" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P12" s="15">
         <v>2</v>
@@ -17292,35 +17934,35 @@
         <v>1</v>
       </c>
       <c r="R12" s="13">
-        <v>0.4</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="S12" s="13">
-        <v>0.46666666666666667</v>
+        <v>0.47058823529411764</v>
       </c>
       <c r="T12" s="13">
-        <v>0.13333333333333333</v>
+        <v>0.11764705882352941</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>Geral!A9</f>
-        <v>miguel miranda</v>
+        <v>lucas volcov</v>
       </c>
       <c r="B13">
         <f>COUNTIF('Player Match Stats'!$C:$C,A13)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13">
         <f>SUMIF('Player Match Stats'!$C:$C,A13,'Player Match Stats'!$F:$F)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <f>SUMIF('Player Match Stats'!$C:$C,A13,'Player Match Stats'!$G:$G)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <f>SUMIF('Player Match Stats'!$C:$C,A13,'Player Match Stats'!$H:$H)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="15">
         <f>SUMIF('Player Match Stats'!$C:$C,A13,'Player Match Stats'!$I:$I)</f>
@@ -17328,15 +17970,15 @@
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>0.35714285714285715</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="H13" s="13">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I13" s="13">
         <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
+        <v>0.2</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" si="3"/>
@@ -17347,37 +17989,37 @@
         <v>8</v>
       </c>
       <c r="L13" t="str">
-        <v>joao</v>
+        <v>douglas b</v>
       </c>
       <c r="M13" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N13" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P13" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q13" s="15">
         <v>1</v>
       </c>
       <c r="R13" s="13">
-        <v>0.38461538461538464</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="S13" s="13">
-        <v>0.46153846153846156</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="T13" s="13">
-        <v>0.15384615384615385</v>
+        <v>0.17647058823529413</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>Geral!A10</f>
-        <v>lucas volcov</v>
+        <v>luciano</v>
       </c>
       <c r="B14">
         <f>COUNTIF('Player Match Stats'!$C:$C,A14)</f>
@@ -17385,11 +18027,11 @@
       </c>
       <c r="C14">
         <f>SUMIF('Player Match Stats'!$C:$C,A14,'Player Match Stats'!$F:$F)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <f>SUMIF('Player Match Stats'!$C:$C,A14,'Player Match Stats'!$G:$G)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <f>SUMIF('Player Match Stats'!$C:$C,A14,'Player Match Stats'!$H:$H)</f>
@@ -17401,11 +18043,11 @@
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="H14" s="13">
         <f t="shared" si="1"/>
-        <v>0.2857142857142857</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="I14" s="13">
         <f t="shared" si="2"/>
@@ -17420,7 +18062,7 @@
         <v>9</v>
       </c>
       <c r="L14" t="str">
-        <v>miguel saddi</v>
+        <v>gabriel diretoria</v>
       </c>
       <c r="M14" s="15">
         <v>17</v>
@@ -17450,7 +18092,7 @@
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>Geral!A11</f>
-        <v>luciano</v>
+        <v>joao</v>
       </c>
       <c r="B15">
         <f>COUNTIF('Player Match Stats'!$C:$C,A15)</f>
@@ -17462,11 +18104,11 @@
       </c>
       <c r="D15">
         <f>SUMIF('Player Match Stats'!$C:$C,A15,'Player Match Stats'!$G:$G)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <f>SUMIF('Player Match Stats'!$C:$C,A15,'Player Match Stats'!$H:$H)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="15">
         <f>SUMIF('Player Match Stats'!$C:$C,A15,'Player Match Stats'!$I:$I)</f>
@@ -17478,11 +18120,11 @@
       </c>
       <c r="H15" s="13">
         <f t="shared" si="1"/>
-        <v>0.35714285714285715</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="2"/>
-        <v>0.21428571428571427</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" si="3"/>
@@ -17493,41 +18135,41 @@
         <v>10</v>
       </c>
       <c r="L15" t="str">
-        <v>miguel miranda</v>
+        <v>alisson</v>
       </c>
       <c r="M15" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N15" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O15" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="15">
         <v>1</v>
       </c>
       <c r="R15" s="13">
-        <v>0.35714285714285715</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="S15" s="13">
-        <v>0.5</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="T15" s="13">
-        <v>0.14285714285714285</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>Geral!A12</f>
-        <v>joao</v>
+        <v>miguel miranda</v>
       </c>
       <c r="B16">
         <f>COUNTIF('Player Match Stats'!$C:$C,A16)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16">
         <f>SUMIF('Player Match Stats'!$C:$C,A16,'Player Match Stats'!$F:$F)</f>
@@ -17535,7 +18177,7 @@
       </c>
       <c r="D16">
         <f>SUMIF('Player Match Stats'!$C:$C,A16,'Player Match Stats'!$G:$G)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <f>SUMIF('Player Match Stats'!$C:$C,A16,'Player Match Stats'!$H:$H)</f>
@@ -17547,15 +18189,15 @@
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>0.38461538461538464</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="H16" s="13">
         <f t="shared" si="1"/>
-        <v>0.46153846153846156</v>
+        <v>0.5</v>
       </c>
       <c r="I16" s="13">
         <f t="shared" si="2"/>
-        <v>0.15384615384615385</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" si="3"/>
@@ -17566,16 +18208,16 @@
         <v>11</v>
       </c>
       <c r="L16" t="str">
-        <v>diego</v>
+        <v>miguel miranda</v>
       </c>
       <c r="M16" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P16" s="15">
         <v>2</v>
@@ -17584,13 +18226,13 @@
         <v>1</v>
       </c>
       <c r="R16" s="13">
-        <v>0.26666666666666666</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="S16" s="13">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="T16" s="13">
-        <v>0.13333333333333333</v>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -17600,7 +18242,7 @@
       </c>
       <c r="B17">
         <f>COUNTIF('Player Match Stats'!$C:$C,A17)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17">
         <f>SUMIF('Player Match Stats'!$C:$C,A17,'Player Match Stats'!$F:$F)</f>
@@ -17608,7 +18250,7 @@
       </c>
       <c r="D17">
         <f>SUMIF('Player Match Stats'!$C:$C,A17,'Player Match Stats'!$G:$G)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <f>SUMIF('Player Match Stats'!$C:$C,A17,'Player Match Stats'!$H:$H)</f>
@@ -17620,32 +18262,51 @@
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
-        <v>0.58333333333333337</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="H17" s="13">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="I17" s="13">
         <f t="shared" si="2"/>
-        <v>8.3333333333333329E-2</v>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" si="3"/>
         <v>✅ SIM</v>
       </c>
-      <c r="K17" t="str">
+      <c r="K17">
         <f>IF(L17&lt;&gt;"",12,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="L17" t="str">
+        <v>diego</v>
+      </c>
+      <c r="M17" s="15">
+        <v>17</v>
+      </c>
+      <c r="N17" s="15">
+        <v>5</v>
+      </c>
+      <c r="O17" s="15">
+        <v>9</v>
+      </c>
+      <c r="P17" s="15">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="15">
+        <v>1</v>
+      </c>
+      <c r="R17" s="13">
+        <v>0.3125</v>
+      </c>
+      <c r="S17" s="13">
+        <v>0.5625</v>
+      </c>
+      <c r="T17" s="13">
+        <v>0.125</v>
+      </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
@@ -17654,7 +18315,7 @@
       </c>
       <c r="B18">
         <f>COUNTIF('Player Match Stats'!$C:$C,A18)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18">
         <f>SUMIF('Player Match Stats'!$C:$C,A18,'Player Match Stats'!$F:$F)</f>
@@ -17662,7 +18323,7 @@
       </c>
       <c r="D18">
         <f>SUMIF('Player Match Stats'!$C:$C,A18,'Player Match Stats'!$G:$G)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18">
         <f>SUMIF('Player Match Stats'!$C:$C,A18,'Player Match Stats'!$H:$H)</f>
@@ -17674,15 +18335,15 @@
       </c>
       <c r="G18">
         <f t="shared" si="0"/>
-        <v>0.54545454545454541</v>
+        <v>0.5</v>
       </c>
       <c r="H18" s="13">
         <f t="shared" si="1"/>
-        <v>0.18181818181818182</v>
+        <v>0.25</v>
       </c>
       <c r="I18" s="13">
         <f t="shared" si="2"/>
-        <v>0.27272727272727271</v>
+        <v>0.25</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" si="3"/>
@@ -17708,11 +18369,11 @@
       </c>
       <c r="B19">
         <f>COUNTIF('Player Match Stats'!$C:$C,A19)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19">
         <f>SUMIF('Player Match Stats'!$C:$C,A19,'Player Match Stats'!$F:$F)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <f>SUMIF('Player Match Stats'!$C:$C,A19,'Player Match Stats'!$G:$G)</f>
@@ -17728,19 +18389,19 @@
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="H19" s="13">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="I19" s="13">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" si="3"/>
-        <v>❌ NÃO</v>
+        <v>✅ SIM</v>
       </c>
       <c r="K19" t="str">
         <f>IF(L19&lt;&gt;"",14,"")</f>
@@ -17762,11 +18423,11 @@
       </c>
       <c r="B20">
         <f>COUNTIF('Player Match Stats'!$C:$C,A20)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20">
         <f>SUMIF('Player Match Stats'!$C:$C,A20,'Player Match Stats'!$F:$F)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <f>SUMIF('Player Match Stats'!$C:$C,A20,'Player Match Stats'!$G:$G)</f>
@@ -17782,15 +18443,15 @@
       </c>
       <c r="G20">
         <f t="shared" si="0"/>
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="H20" s="13">
         <f t="shared" si="1"/>
-        <v>0.44444444444444442</v>
+        <v>0.4</v>
       </c>
       <c r="I20" s="13">
         <f t="shared" si="2"/>
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" si="3"/>
@@ -17816,11 +18477,11 @@
       </c>
       <c r="B21">
         <f>COUNTIF('Player Match Stats'!$C:$C,A21)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21">
         <f>SUMIF('Player Match Stats'!$C:$C,A21,'Player Match Stats'!$F:$F)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21">
         <f>SUMIF('Player Match Stats'!$C:$C,A21,'Player Match Stats'!$G:$G)</f>
@@ -17836,15 +18497,15 @@
       </c>
       <c r="G21">
         <f t="shared" si="0"/>
-        <v>0.22222222222222221</v>
+        <v>0.3</v>
       </c>
       <c r="H21" s="13">
         <f t="shared" si="1"/>
-        <v>0.55555555555555558</v>
+        <v>0.5</v>
       </c>
       <c r="I21" s="13">
         <f t="shared" si="2"/>
-        <v>0.22222222222222221</v>
+        <v>0.2</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" si="3"/>
@@ -17858,7 +18519,7 @@
       </c>
       <c r="B22">
         <f>COUNTIF('Player Match Stats'!$C:$C,A22)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <f>SUMIF('Player Match Stats'!$C:$C,A22,'Player Match Stats'!$F:$F)</f>
@@ -17866,7 +18527,7 @@
       </c>
       <c r="D22">
         <f>SUMIF('Player Match Stats'!$C:$C,A22,'Player Match Stats'!$G:$G)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <f>SUMIF('Player Match Stats'!$C:$C,A22,'Player Match Stats'!$H:$H)</f>
@@ -17878,15 +18539,15 @@
       </c>
       <c r="G22">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.125</v>
       </c>
       <c r="H22" s="13">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="I22" s="13">
         <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
+        <v>0.125</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" si="3"/>
@@ -17896,7 +18557,7 @@
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>Geral!A19</f>
-        <v>renan</v>
+        <v>jonathan</v>
       </c>
       <c r="B23">
         <f>COUNTIF('Player Match Stats'!$C:$C,A23)</f>
@@ -17904,11 +18565,11 @@
       </c>
       <c r="C23">
         <f>SUMIF('Player Match Stats'!$C:$C,A23,'Player Match Stats'!$F:$F)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <f>SUMIF('Player Match Stats'!$C:$C,A23,'Player Match Stats'!$G:$G)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23">
         <f>SUMIF('Player Match Stats'!$C:$C,A23,'Player Match Stats'!$H:$H)</f>
@@ -17920,11 +18581,11 @@
       </c>
       <c r="G23">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="H23" s="13">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I23" s="13">
         <f t="shared" si="2"/>
@@ -17938,7 +18599,7 @@
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>Geral!A20</f>
-        <v>daniel</v>
+        <v>renan</v>
       </c>
       <c r="B24">
         <f>COUNTIF('Player Match Stats'!$C:$C,A24)</f>
@@ -17954,23 +18615,23 @@
       </c>
       <c r="E24">
         <f>SUMIF('Player Match Stats'!$C:$C,A24,'Player Match Stats'!$H:$H)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="15">
         <f>SUMIF('Player Match Stats'!$C:$C,A24,'Player Match Stats'!$I:$I)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H24" s="13">
         <f t="shared" si="1"/>
-        <v>0.42857142857142855</v>
+        <v>0.5</v>
       </c>
       <c r="I24" s="13">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" si="3"/>
@@ -17980,7 +18641,7 @@
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>Geral!A21</f>
-        <v>osmar</v>
+        <v>daniel</v>
       </c>
       <c r="B25">
         <f>COUNTIF('Player Match Stats'!$C:$C,A25)</f>
@@ -17988,31 +18649,31 @@
       </c>
       <c r="C25">
         <f>SUMIF('Player Match Stats'!$C:$C,A25,'Player Match Stats'!$F:$F)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25">
         <f>SUMIF('Player Match Stats'!$C:$C,A25,'Player Match Stats'!$G:$G)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
         <f>SUMIF('Player Match Stats'!$C:$C,A25,'Player Match Stats'!$H:$H)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="15">
         <f>SUMIF('Player Match Stats'!$C:$C,A25,'Player Match Stats'!$I:$I)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H25" s="13">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="I25" s="13">
         <f t="shared" si="2"/>
-        <v>0.16666666666666666</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" si="3"/>
@@ -18022,11 +18683,11 @@
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>Geral!A22</f>
-        <v>carlao</v>
+        <v>osmar</v>
       </c>
       <c r="B26">
         <f>COUNTIF('Player Match Stats'!$C:$C,A26)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <f>SUMIF('Player Match Stats'!$C:$C,A26,'Player Match Stats'!$F:$F)</f>
@@ -18034,7 +18695,7 @@
       </c>
       <c r="D26">
         <f>SUMIF('Player Match Stats'!$C:$C,A26,'Player Match Stats'!$G:$G)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <f>SUMIF('Player Match Stats'!$C:$C,A26,'Player Match Stats'!$H:$H)</f>
@@ -18046,15 +18707,15 @@
       </c>
       <c r="G26">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H26" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="I26" s="13">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" si="3"/>
@@ -18064,7 +18725,7 @@
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>Geral!A23</f>
-        <v>jonathan</v>
+        <v>carlao</v>
       </c>
       <c r="B27">
         <f>COUNTIF('Player Match Stats'!$C:$C,A27)</f>
@@ -18072,11 +18733,11 @@
       </c>
       <c r="C27">
         <f>SUMIF('Player Match Stats'!$C:$C,A27,'Player Match Stats'!$F:$F)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27">
         <f>SUMIF('Player Match Stats'!$C:$C,A27,'Player Match Stats'!$G:$G)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <f>SUMIF('Player Match Stats'!$C:$C,A27,'Player Match Stats'!$H:$H)</f>
@@ -18088,11 +18749,11 @@
       </c>
       <c r="G27">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H27" s="13">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I27" s="13">
         <f t="shared" si="2"/>
@@ -18190,19 +18851,19 @@
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>Geral!A26</f>
-        <v>lucas lopes</v>
+        <v>gesiel</v>
       </c>
       <c r="B30">
         <f>COUNTIF('Player Match Stats'!$C:$C,A30)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30">
         <f>SUMIF('Player Match Stats'!$C:$C,A30,'Player Match Stats'!$F:$F)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30">
         <f>SUMIF('Player Match Stats'!$C:$C,A30,'Player Match Stats'!$G:$G)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <f>SUMIF('Player Match Stats'!$C:$C,A30,'Player Match Stats'!$H:$H)</f>
@@ -18214,11 +18875,11 @@
       </c>
       <c r="G30">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.75</v>
       </c>
       <c r="H30" s="13">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.25</v>
       </c>
       <c r="I30" s="13">
         <f t="shared" si="2"/>
@@ -18274,7 +18935,7 @@
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>Geral!A28</f>
-        <v>gesiel</v>
+        <v>lucas lopes</v>
       </c>
       <c r="B32">
         <f>COUNTIF('Player Match Stats'!$C:$C,A32)</f>
@@ -18282,11 +18943,11 @@
       </c>
       <c r="C32">
         <f>SUMIF('Player Match Stats'!$C:$C,A32,'Player Match Stats'!$F:$F)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <f>SUMIF('Player Match Stats'!$C:$C,A32,'Player Match Stats'!$G:$G)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
         <f>SUMIF('Player Match Stats'!$C:$C,A32,'Player Match Stats'!$H:$H)</f>
@@ -18298,11 +18959,11 @@
       </c>
       <c r="G32">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H32" s="13">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I32" s="13">
         <f t="shared" si="2"/>
@@ -18316,23 +18977,23 @@
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>Geral!A29</f>
-        <v>everton jr</v>
+        <v>pedro</v>
       </c>
       <c r="B33">
         <f>COUNTIF('Player Match Stats'!$C:$C,A33)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33">
         <f>SUMIF('Player Match Stats'!$C:$C,A33,'Player Match Stats'!$F:$F)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <f>SUMIF('Player Match Stats'!$C:$C,A33,'Player Match Stats'!$G:$G)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <f>SUMIF('Player Match Stats'!$C:$C,A33,'Player Match Stats'!$H:$H)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="15">
         <f>SUMIF('Player Match Stats'!$C:$C,A33,'Player Match Stats'!$I:$I)</f>
@@ -18340,15 +19001,15 @@
       </c>
       <c r="G33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H33" s="13">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I33" s="13">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" si="3"/>
@@ -18358,7 +19019,7 @@
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>Geral!A30</f>
-        <v>carto</v>
+        <v>everton jr</v>
       </c>
       <c r="B34">
         <f>COUNTIF('Player Match Stats'!$C:$C,A34)</f>
@@ -18366,7 +19027,7 @@
       </c>
       <c r="C34">
         <f>SUMIF('Player Match Stats'!$C:$C,A34,'Player Match Stats'!$F:$F)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <f>SUMIF('Player Match Stats'!$C:$C,A34,'Player Match Stats'!$G:$G)</f>
@@ -18374,7 +19035,7 @@
       </c>
       <c r="E34">
         <f>SUMIF('Player Match Stats'!$C:$C,A34,'Player Match Stats'!$H:$H)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="15">
         <f>SUMIF('Player Match Stats'!$C:$C,A34,'Player Match Stats'!$I:$I)</f>
@@ -18382,7 +19043,7 @@
       </c>
       <c r="G34">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H34" s="13">
         <f t="shared" si="1"/>
@@ -18390,7 +19051,7 @@
       </c>
       <c r="I34" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" si="3"/>
@@ -18400,7 +19061,7 @@
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>Geral!A31</f>
-        <v>pedro</v>
+        <v>carto</v>
       </c>
       <c r="B35">
         <f>COUNTIF('Player Match Stats'!$C:$C,A35)</f>
